--- a/4. Supervised Learning (modeling and evaluation)/weights_layer1.xlsx
+++ b/4. Supervised Learning (modeling and evaluation)/weights_layer1.xlsx
@@ -732,1814 +732,1814 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01206295710363183</v>
+        <v>-0.2045440808937595</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1906464965721179</v>
+        <v>0.04123247018977948</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008734171420486282</v>
+        <v>-0.05744479706302821</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.1839908017585135</v>
+        <v>0.01555358163488943</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2572627645813086</v>
+        <v>0.1038707560794675</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.04006759442028091</v>
+        <v>0.1159492973751088</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1751846841411333</v>
+        <v>-0.04390781744234701</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1574141518199982</v>
+        <v>0.01195001294683215</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.156626153672333</v>
+        <v>0.2364775862345874</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1761911799899869</v>
+        <v>0.1652458920308133</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.03827472310626492</v>
+        <v>0.1131677166732875</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.00523864866228527</v>
+        <v>0.03745310084974108</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1484727551583226</v>
+        <v>-0.1034525428832443</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0527932376933186</v>
+        <v>-0.1937463771605065</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.08968575381093824</v>
+        <v>-0.03888153503461737</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04256537961630154</v>
+        <v>2.134441680853038e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.03527698599165558</v>
+        <v>0.2137926534081138</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.1366488185341298</v>
+        <v>-0.1234846372639209</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1101047453665887</v>
+        <v>-0.08299296779769424</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.01426126101579678</v>
+        <v>-0.01964998615340552</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1034046340873072</v>
+        <v>0.2167188378946674</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2161472145921148</v>
+        <v>-0.1965664823293374</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.997388889301581e-07</v>
+        <v>0.06073835035297749</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2017224237550338</v>
+        <v>-0.1646563293260278</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0.1288822817886972</v>
+        <v>-0.06060460506583629</v>
       </c>
       <c r="Z2" t="n">
-        <v>-0.04016342506501856</v>
+        <v>-0.02580360225444462</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.1060471679706807</v>
+        <v>0.1773613726990965</v>
       </c>
       <c r="AB2" t="n">
-        <v>-0.1402813994548196</v>
+        <v>-0.06514676590529257</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.03310468100259829</v>
+        <v>0.001087912831797632</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.094987652320683</v>
+        <v>0.002518833844320967</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.1690551139902161</v>
+        <v>-0.09133654366323458</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1.621016987363925e-06</v>
+        <v>0.1746139784648754</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2433639776880481</v>
+        <v>0.06095462858398761</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0.108086731888861</v>
+        <v>-0.07493745803893495</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.2656236520975216</v>
+        <v>-0.0940852442051676</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.1400439348665012</v>
+        <v>0.01727206541196304</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.003916926027008378</v>
+        <v>0.01876290895816118</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.1377974976116436</v>
+        <v>0.08430337546812568</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.1007132702329158</v>
+        <v>0.2257674910064361</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.007472898324901579</v>
+        <v>0.03502899828956119</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.02719151953293126</v>
+        <v>0.09484269346861315</v>
       </c>
       <c r="AP2" t="n">
-        <v>-0.1388608099396459</v>
+        <v>0.1861274813728311</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0.08863176622278321</v>
+        <v>-0.05690128458583602</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.1018430545545164</v>
+        <v>0.002854715961333412</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.1644992552330047</v>
+        <v>-0.0434755359947584</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.1736501676608874</v>
+        <v>0.09622969875189065</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1160293384292986</v>
+        <v>0.0342801315745648</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0.009430784731490742</v>
+        <v>-0.1271280142559518</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.008993722786702959</v>
+        <v>0.003979207754245084</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1242784901581851</v>
+        <v>0.01660508587359793</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.2251960867329606</v>
+        <v>-0.1429408038718857</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0.1731927160686202</v>
+        <v>-0.1457190572404573</v>
       </c>
       <c r="BA2" t="n">
-        <v>-0.1028913847271289</v>
+        <v>-0.1142146354743312</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.002670637514252762</v>
+        <v>0.03780725064166391</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.1515771004553803</v>
+        <v>0.2484368752392071</v>
       </c>
       <c r="BD2" t="n">
-        <v>-9.913132257329542e-09</v>
+        <v>-0.06204815651902714</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.1308438719879876</v>
+        <v>0.1328173790419188</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.01029171418701422</v>
+        <v>0.1785096373454109</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.2228246529981212</v>
+        <v>-0.08343433141804861</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.06058916511699474</v>
+        <v>0.2056814053111585</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0.1529898484803646</v>
+        <v>-0.1649502446352906</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0.06129104843490263</v>
+        <v>0.01409614197902843</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.033335702974167e-05</v>
+        <v>-0.09574789112521179</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0.06661479847933295</v>
+        <v>-0.1361673909181824</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.03924541782463363</v>
+        <v>-0.0002419159172351492</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0.173118116026022</v>
+        <v>-0.05533180353824163</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.08530586150452198</v>
+        <v>0.05654142641835942</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.0615081031098924</v>
+        <v>-0.02408603115141675</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.1344969546832491</v>
+        <v>0.0165100469635031</v>
       </c>
       <c r="BR2" t="n">
-        <v>5.826456748789595e-05</v>
+        <v>-0.1172623549561175</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0.1492434284077808</v>
+        <v>0.09066383035775864</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.127925894276664</v>
+        <v>0.05268544114498408</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.001128227245495157</v>
+        <v>-0.1607741620617358</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.1351827438090312</v>
+        <v>0.188338860898987</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.1351409656096133</v>
+        <v>0.2358962972889248</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.2333073263721392</v>
+        <v>-0.009124957956324837</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.2536477938900255</v>
+        <v>0.1351171246970385</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-1.033248778689541e-08</v>
+        <v>0.158342555585665</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.02257754882222674</v>
+        <v>-0.1707632155330401</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0.08416688486515081</v>
+        <v>0.06119753442902967</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.04593749494284263</v>
+        <v>-0.03321504520480312</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.07700452030847491</v>
+        <v>0.0338930665676812</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.07621303244146833</v>
+        <v>-0.001870895420446203</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.02413040420030137</v>
+        <v>0.2224462003413684</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.1355396864478255</v>
+        <v>-0.03074901042877062</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.08525971009593299</v>
+        <v>0.08363729678093121</v>
       </c>
       <c r="CI2" t="n">
-        <v>0.1152040412155416</v>
+        <v>-0.2278977380178331</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.05687836702744568</v>
+        <v>-0.2023320756835798</v>
       </c>
       <c r="CK2" t="n">
-        <v>2.749373576461245e-05</v>
+        <v>-0.1667472384140237</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0.0156753272210684</v>
+        <v>-0.08636585572578159</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.2252360197787964</v>
+        <v>-0.07803678445443064</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.1642627802217396</v>
+        <v>-0.05225408204361168</v>
       </c>
       <c r="CO2" t="n">
-        <v>-0.1691043714176356</v>
+        <v>0.1935486536238855</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.0334885445277323</v>
+        <v>-0.2395757672645821</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.1143771007444344</v>
+        <v>-0.03911761549542875</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0.01908061434731458</v>
+        <v>-0.06864371984862357</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0.1289095655517519</v>
+        <v>0.09477335315850934</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.167275274074208</v>
+        <v>8.669165322671374e-07</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0.06739197844697238</v>
+        <v>0.0004124022719169838</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.006589347229658409</v>
+        <v>0.2149498139434174</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-0.04682724454308347</v>
+        <v>-0.2230150802674087</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1017586654962834</v>
+        <v>0.2205575868256861</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1600432880709577</v>
+        <v>0.01888704048725235</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.04226062398012308</v>
+        <v>-0.09463643636292725</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06289911681746127</v>
+        <v>-0.02746328490125495</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1027454047689548</v>
+        <v>-0.01539883466183787</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2052690541346496</v>
+        <v>-0.09051099905395779</v>
       </c>
       <c r="H3" t="n">
-        <v>0.08763687972563783</v>
+        <v>0.03752745397553466</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.01225007957546454</v>
+        <v>0.05222822438325094</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2272613300791071</v>
+        <v>0.2056862554043324</v>
       </c>
       <c r="K3" t="n">
-        <v>-7.101126898797931e-05</v>
+        <v>0.0417286692402595</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2464395691653463</v>
+        <v>0.06224518728972089</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1525689587296899</v>
+        <v>-0.2272681902583204</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.001709827699722147</v>
+        <v>0.1072563746718586</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1436806528712517</v>
+        <v>-0.2171510692140056</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.1155121932764212</v>
+        <v>-0.0827800971893818</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2047352917254028</v>
+        <v>-0.07980538824793822</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.008432649259018002</v>
+        <v>0.1786794847012617</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1045289576465136</v>
+        <v>-0.02826022505869275</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1987405757828508</v>
+        <v>0.1733071450433995</v>
       </c>
       <c r="U3" t="n">
-        <v>0.09037598341479285</v>
+        <v>0.04836324065089448</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1080098276107246</v>
+        <v>0.1750153663449389</v>
       </c>
       <c r="W3" t="n">
-        <v>1.647908348228906e-07</v>
+        <v>-0.1242879349514976</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1557039795400068</v>
+        <v>0.03079114259637045</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1168712719899132</v>
+        <v>-0.0006892146351408036</v>
       </c>
       <c r="Z3" t="n">
-        <v>-0.0606787096986765</v>
+        <v>-0.05105473469280242</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.07451886649788701</v>
+        <v>0.1736612177350765</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0.02351820898044103</v>
+        <v>-0.01515761839118158</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.04313235703478555</v>
+        <v>-0.0008831695553792012</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.1823451708930453</v>
+        <v>8.722767026246678e-07</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.05406981733426161</v>
+        <v>0.1545137559477948</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.01233664823133281</v>
+        <v>0.03420711415069705</v>
       </c>
       <c r="AG3" t="n">
-        <v>-0.09917511289253544</v>
+        <v>-0.038364021918135</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.2263101363105407</v>
+        <v>-0.2280994667122758</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.05519140058625813</v>
+        <v>-0.18901017987537</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.2341733544704873</v>
+        <v>0.02325492831082429</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.1074600182759578</v>
+        <v>-0.04042793695307843</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.09480129932237345</v>
+        <v>0.2123303840719063</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.1870887503768149</v>
+        <v>0.1780800487063637</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.03190973078133068</v>
+        <v>-0.09151380127543443</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.06101091500793635</v>
+        <v>-0.07735531733093991</v>
       </c>
       <c r="AP3" t="n">
-        <v>-0.07670541068768655</v>
+        <v>0.08670351966465956</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.090968161927955</v>
+        <v>0.01436265035381919</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.0663445604455308</v>
+        <v>-0.04961396578644024</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.1214983890418074</v>
+        <v>0.1134310976280269</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.138982375254483</v>
+        <v>-0.03448898957695439</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.084392720542142</v>
+        <v>-0.1975361634352427</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.02101626190344666</v>
+        <v>-0.2353465227612453</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.007702583747350359</v>
+        <v>-0.009008064118693865</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0201684576935424</v>
+        <v>0.1714779665239537</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0.03607882665040055</v>
+        <v>0.1465911609890646</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.02966663371258675</v>
+        <v>-0.09736855644253443</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1948577281092783</v>
+        <v>0.1361058318380058</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.618952038538859e-09</v>
+        <v>-0.2192531330022477</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1309164524175059</v>
+        <v>0.189969501836237</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.02076292199451747</v>
+        <v>0.2132821848641119</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.1287959967578112</v>
+        <v>0.1202083490753202</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.1466483693166757</v>
+        <v>-0.1385888680028188</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.01385356256400149</v>
+        <v>-0.07044408695744687</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0.08198355680077672</v>
+        <v>0.1273876518835606</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.01580848947423682</v>
+        <v>-0.03770239797990543</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.1137732127842656</v>
+        <v>-0.181863283563918</v>
       </c>
       <c r="BK3" t="n">
-        <v>-1.212216654719636e-09</v>
+        <v>0.2147248606213231</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.09534279682589948</v>
+        <v>0.1953558998970499</v>
       </c>
       <c r="BM3" t="n">
-        <v>-0.09170752422908746</v>
+        <v>-0.0008445090624555451</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.009911477371886216</v>
+        <v>0.05007401586354184</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.2091279492353535</v>
+        <v>-0.0887574919528769</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.1724193324204271</v>
+        <v>0.2166137322004305</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.07236956947598389</v>
+        <v>0.05941408846505692</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0.1541702871583092</v>
+        <v>0.2233609143112811</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1411322378637232</v>
+        <v>-0.03054324729750799</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.09977923384169307</v>
+        <v>0.04680837585992438</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0.1112909359898204</v>
+        <v>0.001612413558697027</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.09197433229158171</v>
+        <v>-0.05034693076170822</v>
       </c>
       <c r="BW3" t="n">
-        <v>-0.06283081447986907</v>
+        <v>-0.07927422797311484</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.193117816028748</v>
+        <v>-0.2302240974906471</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.05092546840164882</v>
+        <v>0.1443713589150735</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0.01298862698441787</v>
+        <v>0.1294474623709147</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.03754782387918783</v>
+        <v>-0.1299903779660532</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0.02050543754841515</v>
+        <v>-0.1819034666867078</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0.0415907608009557</v>
+        <v>-0.00376712048158804</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.1731255965559968</v>
+        <v>-0.0003063348500002176</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.05661028496182614</v>
+        <v>-0.09824010338754471</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.1099820946800329</v>
+        <v>-0.0891404223199701</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.1033734549436846</v>
+        <v>0.1780340762282904</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.197144576751276</v>
+        <v>0.1534778011952605</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.1697487028678285</v>
+        <v>0.1030512759317905</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.1365278979640589</v>
+        <v>0.05943981153901533</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0001769900386338166</v>
+        <v>0.1795813753621063</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.03481465136313189</v>
+        <v>-0.0752223692780329</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.1368221932460633</v>
+        <v>0.1169779144785155</v>
       </c>
       <c r="CN3" t="n">
-        <v>-0.1401799823768999</v>
+        <v>-0.01683746011934319</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.1557135230198591</v>
+        <v>0.07116252932226126</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0.03037979526494789</v>
+        <v>0.03203967895314962</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.2274142685743105</v>
+        <v>0.07562667819364471</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.2144331449702965</v>
+        <v>-0.006545460744511766</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.02453816353764758</v>
+        <v>-0.05624021181685195</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.03316730017631459</v>
+        <v>-1.777799034048359e-06</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.1184531921454824</v>
+        <v>-0.002040894528286928</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0.008313864190585215</v>
+        <v>-0.1620364228336282</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-0.001819811723039797</v>
+        <v>0.1302190770688411</v>
       </c>
       <c r="B4" t="n">
-        <v>0.04243171153062197</v>
+        <v>-0.09365754040862155</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.1537150261675052</v>
+        <v>0.157294728458535</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1320284964633957</v>
+        <v>-0.0740039477320753</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1288202079022117</v>
+        <v>0.1866180064243305</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2639016648123679</v>
+        <v>0.1528379096446611</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1345998671151404</v>
+        <v>-0.05682261396281877</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2352417417018462</v>
+        <v>0.0518128650114703</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1587553484215793</v>
+        <v>0.2058910143517009</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.02616680728496827</v>
+        <v>-0.1934096160111622</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0007782997333173548</v>
+        <v>-0.008554063059463801</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1119420281070519</v>
+        <v>0.2081998291376168</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1182198219850418</v>
+        <v>0.1740408790534225</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.009563308303642711</v>
+        <v>0.02197852708021911</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1506792715582653</v>
+        <v>0.198727638030887</v>
       </c>
       <c r="P4" t="n">
-        <v>0.04644953599841726</v>
+        <v>-0.004383746480143001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04496219939754925</v>
+        <v>0.1584622306127045</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.07548154353297877</v>
+        <v>-0.1071214002704949</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.09919773492951924</v>
+        <v>-0.001129031268311741</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1101123319634775</v>
+        <v>-0.05894216657705946</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2081235463480192</v>
+        <v>0.2428574408531317</v>
       </c>
       <c r="V4" t="n">
-        <v>0.01834956122295129</v>
+        <v>0.06854215775882419</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.004032955473557346</v>
+        <v>0.2247063654462276</v>
       </c>
       <c r="X4" t="n">
-        <v>0.05163715971485908</v>
+        <v>0.1523112595080895</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.02489690261288326</v>
+        <v>-0.02527263970846317</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02933509331105792</v>
+        <v>-0.1509538904087702</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1856677875203794</v>
+        <v>-0.04285879600256996</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.2344826578976918</v>
+        <v>0.01831805574335659</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.005599689475984121</v>
+        <v>-0.002729150164177452</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.113724721876053</v>
+        <v>-0.07904147797279419</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.04113966692641148</v>
+        <v>0.2077566761703083</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.1755505077848753</v>
+        <v>-0.001868255521462788</v>
       </c>
       <c r="AG4" t="n">
-        <v>-2.406342446297031e-05</v>
+        <v>-0.07244150108829234</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.01796326951459318</v>
+        <v>0.2243077172401688</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.1046179034266558</v>
+        <v>0.1371106943074034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.1251266243903299</v>
+        <v>0.01796255998551495</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.1368449622964114</v>
+        <v>-0.07581244111718985</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.06536683364606242</v>
+        <v>0.05029600237150443</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.04207151527471861</v>
+        <v>0.1476250114624633</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.1274442293011581</v>
+        <v>-0.0403907969669986</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.1405502910211424</v>
+        <v>0.008828634602953833</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.1214853019661278</v>
+        <v>0.1772373445201372</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.1529741412386412</v>
+        <v>0.1536371405796604</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.08405846951167711</v>
+        <v>-0.01383645975690165</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.004042426552586871</v>
+        <v>-0.2294436660848741</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0.1382777836558532</v>
+        <v>0.1177138674009442</v>
       </c>
       <c r="AU4" t="n">
-        <v>-0.06175451644145356</v>
+        <v>-0.1550308578154405</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.069896425433612e-07</v>
+        <v>0.2206749813612333</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.0101467987463347</v>
+        <v>-0.003485784245523975</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.2013555325691086</v>
+        <v>0.1478643970951283</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.08798344655872636</v>
+        <v>0.01126140707069138</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.1729250912268497</v>
+        <v>0.02367947640027238</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0.2148125078405927</v>
+        <v>0.005674167224502183</v>
       </c>
       <c r="BB4" t="n">
-        <v>-0.0447400950787436</v>
+        <v>0.186187347837223</v>
       </c>
       <c r="BC4" t="n">
-        <v>-0.09729990970899208</v>
+        <v>0.1147593699710485</v>
       </c>
       <c r="BD4" t="n">
-        <v>-0.009009202772662915</v>
+        <v>0.1165266029214433</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.004990887469322379</v>
+        <v>0.2250904422529773</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.1899993542103844</v>
+        <v>0.07955845743488171</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.2327707130823255</v>
+        <v>0.2115078599461327</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.09903355491548198</v>
+        <v>0.1375437237931804</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0.07474311338735699</v>
+        <v>0.2012340118511608</v>
       </c>
       <c r="BJ4" t="n">
-        <v>-0.01767403606388226</v>
+        <v>-0.186304643747326</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0.01092654404979367</v>
+        <v>0.1111303391219327</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0.161415264714486</v>
+        <v>0.0962783469918858</v>
       </c>
       <c r="BM4" t="n">
-        <v>-0.1334519842298938</v>
+        <v>-0.08630254705275714</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.08657095617214065</v>
+        <v>-0.1237457543322954</v>
       </c>
       <c r="BO4" t="n">
-        <v>-0.1907524908986084</v>
+        <v>-0.1092125920048675</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.2024063315732208</v>
+        <v>-0.1518931144460249</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.1830247051036845</v>
+        <v>-0.2045300813855845</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0.1948854954324951</v>
+        <v>0.05482203870378253</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.1372925489559737</v>
+        <v>0.08406114790998165</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.2297077685486902</v>
+        <v>-0.2390996859264191</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.186141062494706</v>
+        <v>0.0405452752564025</v>
       </c>
       <c r="BV4" t="n">
-        <v>-0.06443713980637437</v>
+        <v>0.1308611466502203</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.0007032829088813728</v>
+        <v>0.0374524347681538</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0.1063338714996134</v>
+        <v>0.1046673936048374</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.22795059085532</v>
+        <v>0.1470338222247016</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.1808643091986639</v>
+        <v>0.2503787572076243</v>
       </c>
       <c r="CA4" t="n">
-        <v>-9.485421114598563e-08</v>
+        <v>0.001035964484838313</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.1506582724629889</v>
+        <v>0.1316869839251239</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.006660953796580063</v>
+        <v>0.0001947191105244643</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.1508846140915552</v>
+        <v>-0.08887565965563193</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.0273909349922541</v>
+        <v>0.2347486500755513</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.2065978586568363</v>
+        <v>0.009029955116421823</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.1965344706631239</v>
+        <v>0.1287074853506887</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.1001993519472446</v>
+        <v>0.1943292760299608</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.01074125086667144</v>
+        <v>-0.04247581338920896</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0.1487349241334187</v>
+        <v>0.1048546381624694</v>
       </c>
       <c r="CK4" t="n">
-        <v>-0.009912223907832812</v>
+        <v>-0.1653846741597686</v>
       </c>
       <c r="CL4" t="n">
-        <v>-0.005589472511977151</v>
+        <v>-0.06767835434955166</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.1806961522366946</v>
+        <v>-0.208624206873937</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.08753462712910873</v>
+        <v>0.2432270304288666</v>
       </c>
       <c r="CO4" t="n">
-        <v>-0.01357752939242384</v>
+        <v>0.1905935859212122</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.002501722841564765</v>
+        <v>-0.03546620418453147</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.04340186294348093</v>
+        <v>0.1890439914179984</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.009583372565821004</v>
+        <v>-0.1975957641986062</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0.04090029352077125</v>
+        <v>0.02734250164994196</v>
       </c>
       <c r="CT4" t="n">
-        <v>-0.1032037882827082</v>
+        <v>-0.02314257321728717</v>
       </c>
       <c r="CU4" t="n">
-        <v>-0.2201309112553492</v>
+        <v>-0.004283189240206989</v>
       </c>
       <c r="CV4" t="n">
-        <v>-0.2272347492382193</v>
+        <v>0.2113965726817545</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0001759867056900877</v>
+        <v>-0.221087632694812</v>
       </c>
       <c r="B5" t="n">
-        <v>0.07901510250353534</v>
+        <v>0.1893237184530308</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08138586910585886</v>
+        <v>0.1242869289473651</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.02363399948357615</v>
+        <v>-0.05442279639769456</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06624355887354805</v>
+        <v>-0.05048393234247987</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1225738621775418</v>
+        <v>-0.002331175517284493</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1401102659259593</v>
+        <v>-0.1054063249048215</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1249392701341933</v>
+        <v>-0.1377192707162549</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05018896360102227</v>
+        <v>-0.08828648558685025</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1408305608799448</v>
+        <v>-0.1907698325286708</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01894026077657824</v>
+        <v>0.2145174786225256</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1729247025323335</v>
+        <v>-0.1291374009170181</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.005275918775016869</v>
+        <v>-0.2003141577715138</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.04549077596457494</v>
+        <v>0.1899016314091845</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001100657158598837</v>
+        <v>-0.1487413381345888</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.007255434046239386</v>
+        <v>0.02369779758787712</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.006421230952134827</v>
+        <v>0.01522971882343377</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01335464832636117</v>
+        <v>-0.2060645486315421</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.004878590319608957</v>
+        <v>0.0001509176510755318</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2189128043211633</v>
+        <v>-0.1284412369719451</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1018363022393196</v>
+        <v>-0.2159638419658489</v>
       </c>
       <c r="V5" t="n">
-        <v>0.07425271953175962</v>
+        <v>0.1579579232658799</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01183012297752167</v>
+        <v>0.1786684543992701</v>
       </c>
       <c r="X5" t="n">
-        <v>0.001315514440729913</v>
+        <v>0.04789545816414406</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.1798491301986691</v>
+        <v>0.02103120362442254</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.07000276642602679</v>
+        <v>0.1810242625518671</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.09294249585364141</v>
+        <v>-0.0860409958817943</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.02650453251690127</v>
+        <v>0.07196125301396546</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.004741729760621292</v>
+        <v>-0.07502107671463619</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.2138316554035547</v>
+        <v>-0.0061990084518851</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01448399655076016</v>
+        <v>-0.2170360113714161</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.2113901820116893</v>
+        <v>0.02714809931968613</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.05570842174092407</v>
+        <v>-0.03003166676250279</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.0916736772834176</v>
+        <v>-0.1570547553022278</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1406888924148531</v>
+        <v>-0.06514325351267956</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.05833411877350661</v>
+        <v>0.2277296632263997</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.1120771110883353</v>
+        <v>-0.04618160557468808</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.1284960230430666</v>
+        <v>-0.05731102578406815</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.1581270112321968</v>
+        <v>0.1542669335416071</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.1893857810520408</v>
+        <v>0.009843994008964489</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.04999417852032763</v>
+        <v>0.1230945835903431</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.1307654786644313</v>
+        <v>0.09978815165282562</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.1111540864966672</v>
+        <v>-0.09109192383536374</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.1202616185121186</v>
+        <v>-2.299160163345539e-06</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.1822814569816207</v>
+        <v>0.1787098069437567</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.1031024539980704</v>
+        <v>0.09067802193251839</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.004815511230843036</v>
+        <v>0.03837899238863297</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.002271308158908677</v>
+        <v>-0.08633244008214523</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.005354345447792838</v>
+        <v>0.03366587981682244</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1277016927539518</v>
+        <v>-0.1728902426985343</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.03459796965765281</v>
+        <v>-0.05395226067980224</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.145827583454798</v>
+        <v>-0.03606520190315705</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.07766444851300888</v>
+        <v>-0.02115611152054966</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.945540970166781e-05</v>
+        <v>0.2090383071041351</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.06477899932918274</v>
+        <v>0.218488266607767</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.04414861487852892</v>
+        <v>-0.1863880740745906</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.05522266488437085</v>
+        <v>-0.01416955967808994</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.08656248058212225</v>
+        <v>0.0046221531284295</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.09324057257590498</v>
+        <v>-0.1763754833932926</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.1150846296306748</v>
+        <v>-0.05389821766061344</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.05816995324537836</v>
+        <v>-0.06078276123410822</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.08262262324690055</v>
+        <v>0.1299026570039848</v>
       </c>
       <c r="BK5" t="n">
-        <v>-1.368138326586885e-07</v>
+        <v>0.2197648506450861</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.07083749489224021</v>
+        <v>0.01929085321288778</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.171763629577571</v>
+        <v>0.002691376215068435</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.03097305939364584</v>
+        <v>0.06142058589547932</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.1505147674605223</v>
+        <v>0.2201260055876194</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.2461446247586346</v>
+        <v>0.03063044353502777</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.1497144797721077</v>
+        <v>0.03386843347745239</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.02262014438826881</v>
+        <v>0.2345957373338323</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.2275524046515297</v>
+        <v>0.1581510539376649</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.08410719225549479</v>
+        <v>-0.1174426818604613</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.1440509655951012</v>
+        <v>0.1488856976215344</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.02698781152693858</v>
+        <v>0.1656364759759091</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.1255661825148008</v>
+        <v>0.008628916292587241</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.2352441647001732</v>
+        <v>0.1235227900089011</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.2014090919903284</v>
+        <v>-0.2149241153219143</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.1968188313606157</v>
+        <v>0.1707806665225368</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.03468564992728689</v>
+        <v>0.1395609494674696</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.2068791957595782</v>
+        <v>0.02996244037203324</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.00325633912640034</v>
+        <v>-0.01961960969759829</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.009425748569813501</v>
+        <v>-0.08749103314328799</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.1282547428148668</v>
+        <v>-0.1547818112085434</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.07804239839447859</v>
+        <v>0.08137250606000315</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.06189199008669719</v>
+        <v>-0.1544472818240273</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.2399926249133533</v>
+        <v>-0.01929405040791465</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.05559811626234558</v>
+        <v>0.130708326766858</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.01663988276224381</v>
+        <v>0.2203456556285178</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.009554814728817428</v>
+        <v>-0.1185600660017609</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.04214736187459611</v>
+        <v>-0.05550750157791445</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0309209622701336</v>
+        <v>0.07478440515456919</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.02483044271784174</v>
+        <v>-0.137291186056763</v>
       </c>
       <c r="CO5" t="n">
-        <v>0.06217018729988152</v>
+        <v>-0.09421051325391303</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.02612286334567044</v>
+        <v>0.04229424549437763</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.08098197475777427</v>
+        <v>0.05154573444336871</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.02607984894913983</v>
+        <v>0.1678079199510697</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.04433384116549136</v>
+        <v>0.06035205151721304</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.1300733875593457</v>
+        <v>-0.06348957687907286</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.01698919522581877</v>
+        <v>-0.006407407859736074</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.01163334018428189</v>
+        <v>-0.06302507901207625</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0001355542168081236</v>
+        <v>0.1268506429245349</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.2232197048460878</v>
+        <v>-0.1225345729062994</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1621986182657565</v>
+        <v>0.1075578136229863</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2105010274181476</v>
+        <v>-0.01130710116343227</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.179830667487804</v>
+        <v>-0.0181253713586505</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1601779621974382</v>
+        <v>-0.0144567429666965</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1694903589690197</v>
+        <v>0.1515094052913629</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.09543277232336246</v>
+        <v>0.177787433472883</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08093985090006293</v>
+        <v>-0.03510082299377411</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04812164031620415</v>
+        <v>0.1373067170621557</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01108704963913727</v>
+        <v>-0.1629810446221217</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.04607839930570432</v>
+        <v>-0.06356459931472722</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08917780406270449</v>
+        <v>-0.1885232511249585</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.923617344483725e-07</v>
+        <v>-0.1790974228119746</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2130126398658778</v>
+        <v>0.07289715724264983</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1967079603683003</v>
+        <v>-0.02482680565488142</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.02519010474426222</v>
+        <v>-0.1401435582913036</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1185760506038663</v>
+        <v>-0.05237180663307961</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.05564954032147969</v>
+        <v>-4.794457216272531e-06</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1936890652951836</v>
+        <v>0.1870142017860693</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01243761436089176</v>
+        <v>-0.1236613767170426</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2466712186016666</v>
+        <v>0.1904743881148183</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.387316113505296e-09</v>
+        <v>0.1856392833336507</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1262071376167893</v>
+        <v>0.2262378928132143</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.1048924397086013</v>
+        <v>-0.05970977022358175</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.2212252551298555</v>
+        <v>0.02378420588202782</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.09879671677009505</v>
+        <v>0.01105404051892754</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1164257915805503</v>
+        <v>-0.1313903513546205</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.002480383877786069</v>
+        <v>-0.09821032076649003</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.09705970729979545</v>
+        <v>-0.03300536537226924</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.1105355809136516</v>
+        <v>0.1030303116553497</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.06487162757477224</v>
+        <v>0.05715907740024796</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.1831532767912057</v>
+        <v>-0.01537076079566325</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.1794718010487185</v>
+        <v>-0.01499415410359598</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.1406141775579406</v>
+        <v>0.07446011165054005</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.02901982585819247</v>
+        <v>0.2205532648543674</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.1488015541761786</v>
+        <v>-0.005097282160872277</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.1216590414483477</v>
+        <v>0.1508066239542758</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.2229979934973681</v>
+        <v>-0.1068982756987013</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.07708101012352447</v>
+        <v>-0.006538173135403031</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.03733364215096276</v>
+        <v>0.001486420001186026</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.1099956970091424</v>
+        <v>0.07893270938747456</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.05011280138485784</v>
+        <v>0.0786384707676869</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.07273379670544437</v>
+        <v>-0.02539012067603471</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.07515277397244881</v>
+        <v>0.1542710313232153</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.08303500595718129</v>
+        <v>0.129924908388172</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.2383673590096551</v>
+        <v>0.2258146660180373</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.03606466796626987</v>
+        <v>0.1203763448595513</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.252127704705398e-08</v>
+        <v>-0.0757163040837331</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.02096922203486851</v>
+        <v>-0.1885226444740632</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.07110671889142244</v>
+        <v>0.07166461097767857</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.1699745484628909</v>
+        <v>-0.08082791530290979</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.2058666721151231</v>
+        <v>-0.1941913080581224</v>
       </c>
       <c r="BB6" t="n">
-        <v>-4.505128284018626e-05</v>
+        <v>0.07074073933263117</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.095314772802155</v>
+        <v>0.1960394307721268</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.003323556724375361</v>
+        <v>-0.1416869675187692</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.01296927423038381</v>
+        <v>0.07969096632208067</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.1602001547615332</v>
+        <v>-0.190678649990935</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.02556589716249271</v>
+        <v>-0.1330710884578043</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.2173930914882428</v>
+        <v>-0.01035898624653788</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.1940182010969766</v>
+        <v>0.1418052812767829</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.08799334438420638</v>
+        <v>0.182862306284604</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.01249023783771295</v>
+        <v>0.07119659096753385</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.1615555286836603</v>
+        <v>0.1338964415990537</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.2138944585369806</v>
+        <v>-0.04580826459704988</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.08309119355195051</v>
+        <v>-0.04899461887307938</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.06305654133678661</v>
+        <v>0.0719299287068115</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.1246946455597431</v>
+        <v>-0.1655165961556102</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.1039545628716166</v>
+        <v>0.08353419983009891</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.1714826206060646</v>
+        <v>-0.01388988725239587</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.03671517987140906</v>
+        <v>-0.1609031983811421</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.2056092798479409</v>
+        <v>0.08577919631480517</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.04063151122873664</v>
+        <v>0.1365576632266065</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.08347431052175906</v>
+        <v>0.2120817520123946</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.1816777532394666</v>
+        <v>0.01206707759869844</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.02795356009208404</v>
+        <v>-0.05309464718245922</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.03690538990462513</v>
+        <v>-0.1099684464357374</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.02248693619302324</v>
+        <v>0.1401916953727407</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.01341457051651808</v>
+        <v>-0.1005030836862385</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.1804853282572641</v>
+        <v>-0.02695134207361548</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.001335357023918836</v>
+        <v>1.153499727645211e-05</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.1316905629471002</v>
+        <v>0.002355571618507808</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.02020709266278066</v>
+        <v>-0.1216881018204153</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.09023542728545032</v>
+        <v>0.05032178777213112</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.1780510417126419</v>
+        <v>-0.09685411125422147</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.1058375687782623</v>
+        <v>-0.2164232633407724</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.1193129236007349</v>
+        <v>-0.1100586293270803</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.03964517073103899</v>
+        <v>0.1908510633956385</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.05380932340243494</v>
+        <v>-0.05999446730561891</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.02320390013199751</v>
+        <v>0.001041980772732608</v>
       </c>
       <c r="CM6" t="n">
-        <v>-0.1682005953975514</v>
+        <v>0.2136547375462594</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.05874479829892044</v>
+        <v>0.006627617844609033</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.01438589308368313</v>
+        <v>0.1487087386069967</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.01893227956810737</v>
+        <v>0.02177116046009402</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.2161163882987807</v>
+        <v>-0.01178963620802933</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.06800457521968351</v>
+        <v>0.09292691130588951</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.06366901481197208</v>
+        <v>0.04591087889992487</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.1254455468674224</v>
+        <v>-0.01515842374485335</v>
       </c>
       <c r="CU6" t="n">
-        <v>-0.06847157010893826</v>
+        <v>-0.003949708301769449</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.04730109265214471</v>
+        <v>-0.1995297288915575</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.05235068697337936</v>
+        <v>0.1720885519644806</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01248623651401232</v>
+        <v>-0.1941059095327732</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0799842237494594</v>
+        <v>-0.04850659356927282</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1955287575151147</v>
+        <v>0.08603408672231823</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1493778376010789</v>
+        <v>-0.07653401256615265</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2651613629450593</v>
+        <v>-0.1115464805347269</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1306669979827538</v>
+        <v>0.00042039414650327</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.09077782344781131</v>
+        <v>-0.1422465433963239</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2879120972544238</v>
+        <v>0.1630729934297223</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.06068913614571898</v>
+        <v>0.1774686270817959</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0145876716120496</v>
+        <v>0.2135236175840902</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1580186877258653</v>
+        <v>-0.1007185982918934</v>
       </c>
       <c r="M7" t="n">
-        <v>0.09006372317558525</v>
+        <v>-0.08474255898365185</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.03399021988094608</v>
+        <v>0.1294603179530238</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0877851431277607</v>
+        <v>-0.1726586613524621</v>
       </c>
       <c r="P7" t="n">
-        <v>-6.749342675984093e-05</v>
+        <v>9.287161433321272e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0003830446009412988</v>
+        <v>-0.01367956944320274</v>
       </c>
       <c r="R7" t="n">
-        <v>0.08536128349759418</v>
+        <v>0.091134798081383</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1110100898205196</v>
+        <v>0.03916873720782494</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1259710107386707</v>
+        <v>0.09934316015384237</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1244145334328686</v>
+        <v>0.1212065204803199</v>
       </c>
       <c r="V7" t="n">
-        <v>0.004144859598992745</v>
+        <v>-0.001498089728470202</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02148781675424508</v>
+        <v>0.01973648253149022</v>
       </c>
       <c r="X7" t="n">
-        <v>-8.328859911609379e-08</v>
+        <v>0.1665426407542146</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.2325167753686226</v>
+        <v>0.05918354543866991</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2316560806963688</v>
+        <v>-0.02223716857729918</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.02174999706256894</v>
+        <v>0.2294698440183077</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.1166646216475104</v>
+        <v>-0.1963924149916227</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.0002514371602142248</v>
+        <v>3.265562167584118e-05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.1152383201073488</v>
+        <v>-0.033133503134516</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.1276401177582209</v>
+        <v>0.07164474744425769</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.07124377447466698</v>
+        <v>0.2324655410402982</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.2108449939158397</v>
+        <v>1.639404412706459e-06</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.1342777303311771</v>
+        <v>0.1338747346271371</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.1649904808864916</v>
+        <v>0.1884904118404448</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.08687388636546137</v>
+        <v>-0.1770837822128655</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.1990897446757212</v>
+        <v>-0.08201572923878271</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.2154513475850459</v>
+        <v>-0.1044692307112989</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.1059339734144657</v>
+        <v>-0.1344700710653293</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.1161171145247481</v>
+        <v>0.05212734651037772</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.1234182113060785</v>
+        <v>-0.05698955965570048</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.1210911559049662</v>
+        <v>-0.1822741777244785</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.02987266070335852</v>
+        <v>0.1059999174530678</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.2390738009348743</v>
+        <v>-0.02545380160677528</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.0915310227037523</v>
+        <v>0.07562315302971845</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.2115208980932344</v>
+        <v>0.07174489205877789</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.2464024576069417</v>
+        <v>-0.1509970886464621</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.105488706090586e-09</v>
+        <v>-0.1692289375554507</v>
       </c>
       <c r="AW7" t="n">
-        <v>-3.863259448890296e-05</v>
+        <v>0.02970307080584763</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.2170922406437102</v>
+        <v>-0.1268612388782521</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.01869979877676926</v>
+        <v>-0.0680361759171824</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.2007843034648459</v>
+        <v>2.050095779435629e-06</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.09471201255349344</v>
+        <v>0.09741854387814639</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.001374279599651618</v>
+        <v>0.0715084880167197</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.06600392737518058</v>
+        <v>-0.1767257458916976</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.007147505810669248</v>
+        <v>0.04645617809045489</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.2000251612718211</v>
+        <v>-0.01609740595331864</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.1761844824268124</v>
+        <v>0.005138382293225055</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.2130447323273859</v>
+        <v>0.2339314954967082</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.1217887885370826</v>
+        <v>-0.04666518039627048</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0.07549182715300484</v>
+        <v>-0.1694102529503266</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0946242620270256</v>
+        <v>0.0654722266096758</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.01936459446141201</v>
+        <v>-0.07181524056937219</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.1753691185114184</v>
+        <v>0.2060606074283193</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.08884730369598666</v>
+        <v>-0.003172005928376005</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.2119148863003882</v>
+        <v>0.2024181399906847</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.05293044173208709</v>
+        <v>0.2264436937447744</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.1603767501489385</v>
+        <v>-0.1196075487089149</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.022084316861575</v>
+        <v>0.248594295337948</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0.01995683525407371</v>
+        <v>0.01182620392551481</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.02741155686853818</v>
+        <v>-0.06678792199078032</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.04815855284393827</v>
+        <v>-0.1890776987561112</v>
       </c>
       <c r="BU7" t="n">
-        <v>-0.02586754239405547</v>
+        <v>-0.1390444027577654</v>
       </c>
       <c r="BV7" t="n">
-        <v>-0.04244317320241004</v>
+        <v>-0.05286804207535453</v>
       </c>
       <c r="BW7" t="n">
-        <v>-1.905467700529948e-07</v>
+        <v>-0.05599344083842299</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.04836482639847016</v>
+        <v>-0.1338438478400125</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.06619016208473615</v>
+        <v>0.06580813513358087</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.1364635704691657</v>
+        <v>0.0736400179911791</v>
       </c>
       <c r="CA7" t="n">
-        <v>9.072163965472468e-07</v>
+        <v>0.07096990378259856</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0.0285065049081073</v>
+        <v>-0.2048767942625139</v>
       </c>
       <c r="CC7" t="n">
-        <v>8.165649596655629e-07</v>
+        <v>-0.006383303444131931</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.05254130111656999</v>
+        <v>8.632778247954455e-06</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.08998324025227655</v>
+        <v>0.2180761231639428</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.1864869153066759</v>
+        <v>-0.1771484326900135</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.005146588032678496</v>
+        <v>0.08822086186613164</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.06188617976060262</v>
+        <v>0.1777227973452169</v>
       </c>
       <c r="CI7" t="n">
-        <v>-0.2320301079387196</v>
+        <v>-0.0654723995174829</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.05602859720051166</v>
+        <v>-0.1292019398934391</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.01436065185771154</v>
+        <v>0.03740206645645576</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.02285769856931923</v>
+        <v>1.498744213993985e-06</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0385888607389491</v>
+        <v>-0.2196983147126129</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.02531356554427807</v>
+        <v>0.2308562158862973</v>
       </c>
       <c r="CO7" t="n">
-        <v>-0.2281647253594975</v>
+        <v>0.02145735792290236</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.03697708118973191</v>
+        <v>-0.2165306890408143</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.07221462109541121</v>
+        <v>-0.1218110022627911</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.004985690955999503</v>
+        <v>0.142589766873971</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.07068672027930804</v>
+        <v>-0.05156964156598078</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.231563967261218</v>
+        <v>0.05279698370693703</v>
       </c>
       <c r="CU7" t="n">
-        <v>0.1790563043444776</v>
+        <v>3.903514802956876e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0.05504382545547491</v>
+        <v>0.02310147297543668</v>
       </c>
     </row>
   </sheetData>
